--- a/Outputs/Scenarios/PtX_demand_LT_Ammonia.xlsx
+++ b/Outputs/Scenarios/PtX_demand_LT_Ammonia.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.003207264563663378</v>
       </c>
       <c r="K16" t="n">
-        <v>0.001908980623117159</v>
+        <v>0.002073255167090504</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>0.0004290013576633362</v>
       </c>
     </row>
     <row r="18">
@@ -1148,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.003817961246234319</v>
+        <v>0.00343201086130669</v>
       </c>
     </row>
     <row r="20">
@@ -1481,7 +1481,7 @@
         <v>4.62112533740057e-05</v>
       </c>
       <c r="K28" t="n">
-        <v>0.0006363268743723866</v>
+        <v>0.0004290013576633362</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.004747964713591852</v>
       </c>
       <c r="K30" t="n">
-        <v>0.01030217745566235</v>
+        <v>0.01118871631465711</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>0.002315187520421738</v>
       </c>
     </row>
     <row r="32">
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.02060435491132469</v>
+        <v>0.0185215001633739</v>
       </c>
     </row>
     <row r="34">
@@ -1999,7 +1999,7 @@
         <v>0.0002498928796627291</v>
       </c>
       <c r="K42" t="n">
-        <v>0.003434059151887449</v>
+        <v>0.002315187520421738</v>
       </c>
     </row>
     <row r="43">
